--- a/untranslated/downloads/data-excel/8.1.1.xlsx
+++ b/untranslated/downloads/data-excel/8.1.1.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="15465" windowHeight="12255"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12135"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -314,7 +314,7 @@
     <xf numFmtId="165" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -374,6 +374,9 @@
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="19" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="20">
@@ -698,7 +701,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q13"/>
+  <dimension ref="A1:R13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="3" width="37.5703125" style="4" customWidth="1"/>
@@ -706,7 +709,7 @@
     <col min="18" max="16384" width="9.140625" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="30" customHeight="1">
+    <row r="1" spans="1:18" ht="30" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>8</v>
       </c>
@@ -725,7 +728,7 @@
       <c r="J1" s="3"/>
       <c r="K1" s="3"/>
     </row>
-    <row r="2" spans="1:17">
+    <row r="2" spans="1:18">
       <c r="A2" s="8" t="s">
         <v>5</v>
       </c>
@@ -744,7 +747,7 @@
       <c r="J2" s="3"/>
       <c r="K2" s="3"/>
     </row>
-    <row r="3" spans="1:17" ht="15.75" thickBot="1">
+    <row r="3" spans="1:18" ht="15.75" thickBot="1">
       <c r="A3" s="3"/>
       <c r="B3" s="19"/>
       <c r="C3" s="19"/>
@@ -756,8 +759,9 @@
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
       <c r="K3" s="3"/>
+      <c r="R3"/>
     </row>
-    <row r="4" spans="1:17" ht="15.75" thickBot="1">
+    <row r="4" spans="1:18" ht="15.75" thickBot="1">
       <c r="A4" s="5" t="s">
         <v>2</v>
       </c>
@@ -809,8 +813,11 @@
       <c r="Q4" s="14">
         <v>2023</v>
       </c>
+      <c r="R4" s="14">
+        <v>2024</v>
+      </c>
     </row>
-    <row r="5" spans="1:17" ht="31.5" customHeight="1" thickBot="1">
+    <row r="5" spans="1:18" ht="31.5" customHeight="1" thickBot="1">
       <c r="A5" s="10" t="s">
         <v>4</v>
       </c>
@@ -862,8 +869,11 @@
       <c r="Q5" s="17">
         <v>7.1</v>
       </c>
+      <c r="R5" s="22">
+        <v>9.6</v>
+      </c>
     </row>
-    <row r="6" spans="1:17" customFormat="1" ht="37.5" customHeight="1">
+    <row r="6" spans="1:18" customFormat="1" ht="37.5" customHeight="1">
       <c r="A6" s="20" t="s">
         <v>13</v>
       </c>
@@ -884,12 +894,12 @@
       <c r="L6" s="18"/>
       <c r="M6" s="18"/>
     </row>
-    <row r="10" spans="1:17">
+    <row r="10" spans="1:18">
       <c r="I10" s="4" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:17">
+    <row r="13" spans="1:18">
       <c r="I13" s="4" t="s">
         <v>12</v>
       </c>
